--- a/hall/resources/sample/popUpGetWay.xlsx
+++ b/hall/resources/sample/popUpGetWay.xlsx
@@ -130,7 +130,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="40">
   <si>
     <t>id</t>
   </si>
@@ -250,27 +250,6 @@
   </si>
   <si>
     <t>私人房间</t>
-  </si>
-  <si>
-    <t>刮刮卡</t>
-  </si>
-  <si>
-    <t>d_icon_gift.png</t>
-  </si>
-  <si>
-    <t>刮刮卡礼包</t>
-  </si>
-  <si>
-    <t>X_UICashCow_0</t>
-  </si>
-  <si>
-    <t>task_GoldMineTycoon.png</t>
-  </si>
-  <si>
-    <t>任意游戏</t>
-  </si>
-  <si>
-    <t>跳转到大厅即可</t>
   </si>
 </sst>
 </file>
@@ -1607,73 +1586,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" s="2" customFormat="1" spans="1:11">
-      <c r="A11" s="2">
-        <v>1201</v>
-      </c>
-      <c r="B11" s="2">
-        <v>1022502</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" s="2">
-        <v>1</v>
-      </c>
-      <c r="E11" s="2">
-        <v>3010013</v>
-      </c>
-      <c r="F11" s="2">
-        <v>3010014</v>
-      </c>
-      <c r="H11" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" s="2" customFormat="1" spans="1:11">
-      <c r="A12" s="2">
-        <v>1202</v>
-      </c>
-      <c r="B12" s="2">
-        <v>1022502</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="2">
-        <v>4</v>
-      </c>
-      <c r="E12" s="2">
-        <v>3010015</v>
-      </c>
-      <c r="F12" s="2">
-        <v>3010016</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H12" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
+    <row r="11" s="2" customFormat="1"/>
+    <row r="12" s="2" customFormat="1"/>
     <row r="13" s="2" customFormat="1"/>
     <row r="14" s="2" customFormat="1"/>
     <row r="15" s="2" customFormat="1"/>

--- a/hall/resources/sample/popUpGetWay.xlsx
+++ b/hall/resources/sample/popUpGetWay.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="popUpGetWay" sheetId="1" r:id="rId1"/>
@@ -80,7 +80,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="I1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -103,7 +103,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="J1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -130,7 +130,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="47">
   <si>
     <t>id</t>
   </si>
@@ -153,6 +153,9 @@
     <t>打开界面名称</t>
   </si>
   <si>
+    <t>打开界面需要导入的脚本</t>
+  </si>
+  <si>
     <t>是否开启</t>
   </si>
   <si>
@@ -162,15 +165,15 @@
     <t>int</t>
   </si>
   <si>
-    <t>map&lt;string{_}string&gt;{;}</t>
+    <t>list&lt;string&gt;{_}</t>
+  </si>
+  <si>
+    <t>string</t>
   </si>
   <si>
     <t>bool</t>
   </si>
   <si>
-    <t>string</t>
-  </si>
-  <si>
     <t>itemId</t>
   </si>
   <si>
@@ -186,6 +189,9 @@
     <t>uiName</t>
   </si>
   <si>
+    <t>require</t>
+  </si>
+  <si>
     <t>open</t>
   </si>
   <si>
@@ -195,7 +201,10 @@
     <t>金币</t>
   </si>
   <si>
-    <t>9_UICashCow_uiGold</t>
+    <t>9_UIMall_2</t>
+  </si>
+  <si>
+    <t>PlatformHall/UIActivities/UIMall/MVCHead</t>
   </si>
   <si>
     <t>d_icon_sc.png</t>
@@ -210,13 +219,19 @@
     <t>3_UICashCow_0</t>
   </si>
   <si>
+    <t>PlatformHall/UIActivities/UICashCow/MVCHead</t>
+  </si>
+  <si>
     <t>d_icon_facaishu.png</t>
   </si>
   <si>
     <t>摇钱树活动</t>
   </si>
   <si>
-    <t>4_UICashCow_0</t>
+    <t>4_UISavingPot_0</t>
+  </si>
+  <si>
+    <t>PlatformHall/UIActivities/UISavingPot/MVCHead</t>
   </si>
   <si>
     <t>d_icon_piggy_bank.png</t>
@@ -225,7 +240,10 @@
     <t>储钱罐</t>
   </si>
   <si>
-    <t>101_UICashCow_0</t>
+    <t>101_MyCasinoLoading_0</t>
+  </si>
+  <si>
+    <t>PlatformHall/MyCasino/MVCHead</t>
   </si>
   <si>
     <t>d_icon_casino.png</t>
@@ -237,13 +255,16 @@
     <t>钻石</t>
   </si>
   <si>
-    <t>9_UICashCow_uiDiamond</t>
+    <t>9_UIMall_3</t>
   </si>
   <si>
     <t>商城购买钻石</t>
   </si>
   <si>
-    <t>8_UICashCow_0</t>
+    <t>8_UICreatRoom_0</t>
+  </si>
+  <si>
+    <t>PlatformHall/UICreatRoom/MVCHead</t>
   </si>
   <si>
     <t>d_icon_xuanfj.png</t>
@@ -915,7 +936,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -934,6 +955,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1256,7 +1280,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.5" style="3" customWidth="1"/>
@@ -1265,14 +1289,15 @@
     <col min="4" max="4" width="8.875" style="3" customWidth="1"/>
     <col min="5" max="6" width="9.25" style="3" customWidth="1"/>
     <col min="7" max="7" width="25.875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="8.875" style="3" customWidth="1"/>
-    <col min="9" max="9" width="29.5" style="3" customWidth="1"/>
-    <col min="10" max="10" width="12.875" style="3" customWidth="1"/>
-    <col min="11" max="11" width="51.625" style="3" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="3"/>
+    <col min="8" max="8" width="44.1166666666667" style="3" customWidth="1"/>
+    <col min="9" max="9" width="8.875" style="3" customWidth="1"/>
+    <col min="10" max="10" width="29.5" style="3" customWidth="1"/>
+    <col min="11" max="11" width="12.875" style="3" customWidth="1"/>
+    <col min="12" max="12" width="51.625" style="3" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" spans="1:11">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:12">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1294,74 +1319,83 @@
       <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>2</v>
+      <c r="J1" s="6" t="s">
+        <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="L1" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="15" spans="1:9">
+    <row r="2" s="1" customFormat="1" ht="15" spans="1:10">
       <c r="A2" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="6" t="s">
         <v>11</v>
       </c>
+      <c r="H2" s="10" t="s">
+        <v>12</v>
+      </c>
       <c r="I2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="15" spans="1:9">
+    <row r="3" s="1" customFormat="1" ht="15" spans="1:10">
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="6" t="s">
         <v>18</v>
       </c>
+      <c r="H3" s="7" t="s">
+        <v>19</v>
+      </c>
       <c r="I3" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="15" spans="1:12">
+    <row r="4" s="1" customFormat="1" ht="15" spans="1:13">
       <c r="A4" s="5"/>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -1369,13 +1403,14 @@
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
-      <c r="H4" s="6"/>
+      <c r="H4" s="7"/>
       <c r="I4" s="6"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:13">
       <c r="A5" s="2">
         <v>1001</v>
       </c>
@@ -1383,7 +1418,7 @@
         <v>1990000</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
@@ -1395,23 +1430,26 @@
         <v>3010002</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" s="2" t="b">
+        <v>23</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I5" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="J5" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L5" s="2"/>
+        <v>26</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M5" s="2"/>
     </row>
-    <row r="6" s="2" customFormat="1" spans="1:11">
+    <row r="6" s="2" customFormat="1" spans="1:12">
       <c r="A6" s="2">
         <v>1002</v>
       </c>
@@ -1419,7 +1457,7 @@
         <v>1990000</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>
@@ -1431,22 +1469,25 @@
         <v>3010004</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" s="2" t="b">
+        <v>28</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="J6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>24</v>
-      </c>
     </row>
-    <row r="7" s="2" customFormat="1" spans="1:11">
+    <row r="7" s="2" customFormat="1" spans="1:12">
       <c r="A7" s="2">
         <v>1003</v>
       </c>
@@ -1454,7 +1495,7 @@
         <v>1990000</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D7" s="2">
         <v>1</v>
@@ -1466,22 +1507,25 @@
         <v>3010006</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H7" s="2" t="b">
+        <v>32</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I7" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="J7" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" spans="1:11">
+    <row r="8" s="2" customFormat="1" spans="1:12">
       <c r="A8" s="2">
         <v>1004</v>
       </c>
@@ -1489,7 +1533,7 @@
         <v>1990000</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D8" s="2">
         <v>2</v>
@@ -1501,22 +1545,25 @@
         <v>3010008</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H8" s="2" t="b">
+        <v>36</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I8" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I8" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="J8" s="2" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" spans="1:11">
+    <row r="9" s="2" customFormat="1" spans="1:12">
       <c r="A9" s="2">
         <v>1101</v>
       </c>
@@ -1524,7 +1571,7 @@
         <v>1980000</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D9" s="2">
         <v>2</v>
@@ -1536,22 +1583,25 @@
         <v>3010010</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H9" s="2" t="b">
+        <v>41</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I9" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I9" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="J9" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" spans="1:11">
+    <row r="10" s="2" customFormat="1" spans="1:12">
       <c r="A10" s="2">
         <v>1102</v>
       </c>
@@ -1559,7 +1609,7 @@
         <v>1980000</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D10" s="2">
         <v>2</v>
@@ -1571,19 +1621,22 @@
         <v>3010012</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H10" s="2" t="b">
+        <v>43</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I10" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I10" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="J10" s="2" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1"/>

--- a/hall/resources/sample/popUpGetWay.xlsx
+++ b/hall/resources/sample/popUpGetWay.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="popUpGetWay" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -130,7 +131,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="46">
   <si>
     <t>id</t>
   </si>
@@ -240,7 +241,25 @@
     <t>储钱罐</t>
   </si>
   <si>
-    <t>101_MyCasinoLoading_0</t>
+    <t>钻石</t>
+  </si>
+  <si>
+    <t>9_UIMall_3</t>
+  </si>
+  <si>
+    <t>商城购买钻石</t>
+  </si>
+  <si>
+    <t>8_UICreatRoom_0</t>
+  </si>
+  <si>
+    <t>PlatformHall/UICreatRoom/MVCHead</t>
+  </si>
+  <si>
+    <t>d_icon_xuanfj.png</t>
+  </si>
+  <si>
+    <t>私人房间</t>
   </si>
   <si>
     <t>PlatformHall/MyCasino/MVCHead</t>
@@ -250,27 +269,6 @@
   </si>
   <si>
     <t>我的赌场</t>
-  </si>
-  <si>
-    <t>钻石</t>
-  </si>
-  <si>
-    <t>9_UIMall_3</t>
-  </si>
-  <si>
-    <t>商城购买钻石</t>
-  </si>
-  <si>
-    <t>8_UICreatRoom_0</t>
-  </si>
-  <si>
-    <t>PlatformHall/UICreatRoom/MVCHead</t>
-  </si>
-  <si>
-    <t>d_icon_xuanfj.png</t>
-  </si>
-  <si>
-    <t>私人房间</t>
   </si>
 </sst>
 </file>
@@ -456,12 +454,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1280,7 +1278,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.5" style="3" customWidth="1"/>
@@ -1297,7 +1295,7 @@
     <col min="13" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" spans="1:12">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:13">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1335,7 +1333,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="15" spans="1:10">
+    <row r="2" s="1" customFormat="1" ht="15" spans="1:13">
       <c r="A2" s="8" t="s">
         <v>10</v>
       </c>
@@ -1365,7 +1363,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="15" spans="1:10">
+    <row r="3" s="1" customFormat="1" ht="15" spans="1:13">
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
@@ -1449,7 +1447,7 @@
       </c>
       <c r="M5" s="2"/>
     </row>
-    <row r="6" s="2" customFormat="1" spans="1:12">
+    <row r="6" s="2" customFormat="1" spans="1:13">
       <c r="A6" s="2">
         <v>1002</v>
       </c>
@@ -1487,7 +1485,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" spans="1:12">
+    <row r="7" s="2" customFormat="1" spans="1:13">
       <c r="A7" s="2">
         <v>1003</v>
       </c>
@@ -1525,74 +1523,74 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" spans="1:12">
+    <row r="8" s="2" customFormat="1" spans="1:13">
       <c r="A8" s="2">
-        <v>1004</v>
+        <v>1101</v>
       </c>
       <c r="B8" s="2">
-        <v>1990000</v>
+        <v>1980000</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="D8" s="2">
         <v>2</v>
       </c>
       <c r="E8" s="2">
-        <v>3010007</v>
+        <v>3010009</v>
       </c>
       <c r="F8" s="2">
-        <v>3010008</v>
+        <v>3010010</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="I8" s="2" t="b">
         <v>1</v>
       </c>
       <c r="J8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" spans="1:12">
+    <row r="9" s="2" customFormat="1" spans="1:13">
       <c r="A9" s="2">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="B9" s="2">
         <v>1980000</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D9" s="2">
         <v>2</v>
       </c>
       <c r="E9" s="2">
-        <v>3010009</v>
+        <v>3010011</v>
       </c>
       <c r="F9" s="2">
-        <v>3010010</v>
+        <v>3010012</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="I9" s="2" t="b">
         <v>1</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>42</v>
@@ -1601,44 +1599,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" spans="1:12">
-      <c r="A10" s="2">
-        <v>1102</v>
-      </c>
-      <c r="B10" s="2">
-        <v>1980000</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" s="2">
-        <v>2</v>
-      </c>
-      <c r="E10" s="2">
-        <v>3010011</v>
-      </c>
-      <c r="F10" s="2">
-        <v>3010012</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I10" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
+    <row r="10" s="2" customFormat="1"/>
     <row r="11" s="2" customFormat="1"/>
     <row r="12" s="2" customFormat="1"/>
     <row r="13" s="2" customFormat="1"/>
@@ -1649,11 +1610,131 @@
     <row r="18" s="2" customFormat="1"/>
     <row r="19" s="2" customFormat="1"/>
     <row r="20" s="2" customFormat="1"/>
-    <row r="21" s="2" customFormat="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="D3:H8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7" outlineLevelCol="7"/>
+  <cols>
+    <col min="4" max="4" width="43.875" customWidth="1"/>
+    <col min="5" max="5" width="5.75" customWidth="1"/>
+    <col min="6" max="6" width="21.5" customWidth="1"/>
+    <col min="7" max="7" width="12.875" customWidth="1"/>
+    <col min="8" max="8" width="36.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="4:8">
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="4:8">
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="4:8">
+      <c r="D5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="4:8">
+      <c r="D6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="4:8">
+      <c r="D7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="4:8">
+      <c r="D8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G8" t="s">
+        <v>42</v>
+      </c>
+      <c r="H8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/hall/resources/sample/popUpGetWay.xlsx
+++ b/hall/resources/sample/popUpGetWay.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="popUpGetWay" sheetId="1" r:id="rId1"/>
@@ -130,8 +130,111 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="D12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1. 活动
+2. 功能
+3. 游戏ID或0  (指定游戏填写ID,0表示任意游戏)
+4. 大厅</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+界面名称为空或0值时，不跳转；
+参数：功能\活动ID_界面名称_页签名称  (当页签名称为0时，只需要打开指定界面即可 不用精准跳转)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1：开启
+0或空：关闭</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+显示途径的图标ICON</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="46">
   <si>
     <t>id</t>
   </si>
@@ -229,46 +332,46 @@
     <t>摇钱树活动</t>
   </si>
   <si>
+    <t>钻石</t>
+  </si>
+  <si>
+    <t>9_UIMall_3</t>
+  </si>
+  <si>
+    <t>商城购买钻石</t>
+  </si>
+  <si>
+    <t>PlatformHall/UIActivities/UISavingPot/MVCHead</t>
+  </si>
+  <si>
+    <t>d_icon_piggy_bank.png</t>
+  </si>
+  <si>
+    <t>储钱罐</t>
+  </si>
+  <si>
+    <t>PlatformHall/MyCasino/MVCHead</t>
+  </si>
+  <si>
+    <t>d_icon_casino.png</t>
+  </si>
+  <si>
+    <t>我的赌场</t>
+  </si>
+  <si>
+    <t>PlatformHall/UICreatRoom/MVCHead</t>
+  </si>
+  <si>
+    <t>d_icon_xuanfj.png</t>
+  </si>
+  <si>
+    <t>私人房间</t>
+  </si>
+  <si>
     <t>4_UISavingPot_0</t>
   </si>
   <si>
-    <t>PlatformHall/UIActivities/UISavingPot/MVCHead</t>
-  </si>
-  <si>
-    <t>d_icon_piggy_bank.png</t>
-  </si>
-  <si>
-    <t>储钱罐</t>
-  </si>
-  <si>
-    <t>钻石</t>
-  </si>
-  <si>
-    <t>9_UIMall_3</t>
-  </si>
-  <si>
-    <t>商城购买钻石</t>
-  </si>
-  <si>
     <t>8_UICreatRoom_0</t>
-  </si>
-  <si>
-    <t>PlatformHall/UICreatRoom/MVCHead</t>
-  </si>
-  <si>
-    <t>d_icon_xuanfj.png</t>
-  </si>
-  <si>
-    <t>私人房间</t>
-  </si>
-  <si>
-    <t>PlatformHall/MyCasino/MVCHead</t>
-  </si>
-  <si>
-    <t>d_icon_casino.png</t>
-  </si>
-  <si>
-    <t>我的赌场</t>
   </si>
 </sst>
 </file>
@@ -454,12 +557,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -938,7 +1041,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -959,6 +1061,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1278,52 +1381,52 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="9.5" style="3" customWidth="1"/>
-    <col min="2" max="2" width="9.25" style="3" customWidth="1"/>
-    <col min="3" max="3" width="7" style="3" customWidth="1"/>
-    <col min="4" max="4" width="8.875" style="3" customWidth="1"/>
-    <col min="5" max="6" width="9.25" style="3" customWidth="1"/>
-    <col min="7" max="7" width="25.875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="44.1166666666667" style="3" customWidth="1"/>
-    <col min="9" max="9" width="8.875" style="3" customWidth="1"/>
-    <col min="10" max="10" width="29.5" style="3" customWidth="1"/>
-    <col min="11" max="11" width="12.875" style="3" customWidth="1"/>
-    <col min="12" max="12" width="51.625" style="3" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="9.5" style="11" customWidth="1"/>
+    <col min="2" max="2" width="9.25" style="11" customWidth="1"/>
+    <col min="3" max="3" width="7" style="11" customWidth="1"/>
+    <col min="4" max="4" width="8.875" style="11" customWidth="1"/>
+    <col min="5" max="6" width="9.25" style="11" customWidth="1"/>
+    <col min="7" max="7" width="25.875" style="11" customWidth="1"/>
+    <col min="8" max="8" width="44.1166666666667" style="11" customWidth="1"/>
+    <col min="9" max="9" width="8.875" style="11" customWidth="1"/>
+    <col min="10" max="10" width="29.5" style="11" customWidth="1"/>
+    <col min="11" max="11" width="12.875" style="11" customWidth="1"/>
+    <col min="12" max="12" width="51.625" style="11" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="15" spans="1:13">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
@@ -1334,79 +1437,79 @@
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="15" spans="1:13">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="8" t="s">
+      <c r="C2" s="5"/>
+      <c r="D2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="15" spans="1:13">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="6" t="s">
+      <c r="C3" s="4"/>
+      <c r="D3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="5" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="15" spans="1:13">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2">
@@ -1487,118 +1590,44 @@
     </row>
     <row r="7" s="2" customFormat="1" spans="1:13">
       <c r="A7" s="2">
-        <v>1003</v>
+        <v>1101</v>
       </c>
       <c r="B7" s="2">
-        <v>1990000</v>
+        <v>1980000</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D7" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="2">
-        <v>3010005</v>
+        <v>3010009</v>
       </c>
       <c r="F7" s="2">
-        <v>3010006</v>
+        <v>3010010</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="I7" s="2" t="b">
         <v>1</v>
       </c>
       <c r="J7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K7" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" spans="1:13">
-      <c r="A8" s="2">
-        <v>1101</v>
-      </c>
-      <c r="B8" s="2">
-        <v>1980000</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" s="2">
-        <v>2</v>
-      </c>
-      <c r="E8" s="2">
-        <v>3010009</v>
-      </c>
-      <c r="F8" s="2">
-        <v>3010010</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I8" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" s="2" customFormat="1" spans="1:13">
-      <c r="A9" s="2">
-        <v>1102</v>
-      </c>
-      <c r="B9" s="2">
-        <v>1980000</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" s="2">
-        <v>2</v>
-      </c>
-      <c r="E9" s="2">
-        <v>3010011</v>
-      </c>
-      <c r="F9" s="2">
-        <v>3010012</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="I9" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
+    <row r="8" customFormat="1"/>
+    <row r="9" s="2" customFormat="1"/>
     <row r="10" s="2" customFormat="1"/>
     <row r="11" s="2" customFormat="1"/>
     <row r="12" s="2" customFormat="1"/>
@@ -1609,7 +1638,6 @@
     <row r="17" s="2" customFormat="1"/>
     <row r="18" s="2" customFormat="1"/>
     <row r="19" s="2" customFormat="1"/>
-    <row r="20" s="2" customFormat="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1621,8 +1649,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="D3:H8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7" outlineLevelCol="7"/>
+  <dimension ref="A3:M17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="4" max="4" width="43.875" customWidth="1"/>
     <col min="5" max="5" width="5.75" customWidth="1"/>
@@ -1631,7 +1659,7 @@
     <col min="8" max="8" width="36.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="4:8">
+    <row r="3" spans="1:13">
       <c r="D3" t="s">
         <v>24</v>
       </c>
@@ -1648,7 +1676,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="4:8">
+    <row r="4" spans="1:13">
       <c r="D4" t="s">
         <v>29</v>
       </c>
@@ -1665,41 +1693,41 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="4:8">
+    <row r="5" spans="1:13">
       <c r="D5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="4:8">
+    <row r="6" spans="1:13">
       <c r="D6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G6" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="H6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="4:8">
+    <row r="7" spans="1:13">
       <c r="D7" t="s">
         <v>24</v>
       </c>
@@ -1710,31 +1738,221 @@
         <v>25</v>
       </c>
       <c r="G7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="H7" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="4:8">
+    <row r="8" spans="1:13">
       <c r="D8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
       </c>
       <c r="F8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="15" spans="1:13">
+      <c r="A12" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="15" spans="1:13">
+      <c r="A13" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="5"/>
+      <c r="D13" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="15" spans="1:13">
+      <c r="A14" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="4"/>
+      <c r="D14" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="15" spans="1:13">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+    </row>
+    <row r="16" s="2" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A16" s="2">
+        <v>1003</v>
+      </c>
+      <c r="B16" s="2">
+        <v>1990000</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="2">
+        <v>1</v>
+      </c>
+      <c r="E16" s="2">
+        <v>3010005</v>
+      </c>
+      <c r="F16" s="2">
+        <v>3010006</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A17" s="2">
+        <v>1102</v>
+      </c>
+      <c r="B17" s="2">
+        <v>1980000</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="2">
+        <v>2</v>
+      </c>
+      <c r="E17" s="2">
+        <v>3010011</v>
+      </c>
+      <c r="F17" s="2">
+        <v>3010012</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="G8" t="s">
+      <c r="I17" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="H8" t="s">
+      <c r="K17" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L17" s="2" t="s">
         <v>27</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>